--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64934_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64934_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6e34e96c1ac64a2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5343d641293148f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.2283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.8080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6301</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.5530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.2851</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -654,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.1879</x:v>
+        <x:v>     15.1887</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.6875</x:v>
+        <x:v>     16.6914</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.6592</x:v>
+        <x:v>     25.6608</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.5172</x:v>
+        <x:v>     16.5179</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.3346</x:v>
+        <x:v>     15.3354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.4226</x:v>
+        <x:v>     16.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.7376</x:v>
+        <x:v>     15.7391</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.7607</x:v>
+        <x:v>     15.7623</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64934_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_64934_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5343d641293148f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R469c8a78c1f848dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0657</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.9895</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3848</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6686</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.8045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.1767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.9299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.5083</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.8333</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.4225</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.6389</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.0545</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.2632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.2721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.3887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.3897</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.2812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.3814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.3539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.3807</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4269</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.0646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.9739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.8146</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.7945</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.8797</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.1234</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.1238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4301</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.3041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.0310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.8895</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.8883</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.0349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.9022</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.1235</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.3790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
